--- a/data/trans_bre/P16A08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A08-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,99</t>
+          <t>0,39; 3,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,22</t>
+          <t>0,22; 3,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,1</t>
+          <t>-0,32; 3,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 3,23</t>
+          <t>-0,09; 3,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,82; 212,18</t>
+          <t>7,85; 207,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 180,3</t>
+          <t>3,09; 178,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 167,97</t>
+          <t>-14,18; 171,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 327,84</t>
+          <t>-13,1; 340,31</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,28</t>
+          <t>0,84; 3,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,02</t>
+          <t>1,2; 4,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,03</t>
+          <t>1,47; 3,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 14,78</t>
+          <t>0,2; 14,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,28; 204,18</t>
+          <t>28,8; 209,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,68; 144,9</t>
+          <t>30,6; 145,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,59; 170,28</t>
+          <t>42,5; 167,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 480,61</t>
+          <t>6,6; 504,31</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,78</t>
+          <t>-2,8; 2,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 5,31</t>
+          <t>-1,62; 5,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 5,61</t>
+          <t>-0,53; 5,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 5,17</t>
+          <t>0,69; 5,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,8; 88,43</t>
+          <t>-51,24; 95,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 142,3</t>
+          <t>-25,66; 143,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 179,8</t>
+          <t>-9,1; 153,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 285,0</t>
+          <t>9,57; 295,99</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,4</t>
+          <t>0,64; 2,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,25</t>
+          <t>1,05; 3,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,27</t>
+          <t>1,26; 3,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 10,46</t>
+          <t>0,83; 10,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,03; 121,72</t>
+          <t>22,13; 120,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,77; 107,06</t>
+          <t>26,65; 100,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,09; 122,11</t>
+          <t>35,81; 124,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,78; 332,06</t>
+          <t>23,25; 385,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A08-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,79</t>
+          <t>2,1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>105,05%</t>
+          <t>128,17%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,03</t>
+          <t>0,35; 3,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 3,4</t>
+          <t>0,11; 3,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 3,07</t>
+          <t>-0,35; 3,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,11</t>
+          <t>0,36; 3,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,85; 207,57</t>
+          <t>9,84; 236,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 178,81</t>
+          <t>1,22; 164,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 171,11</t>
+          <t>-12,87; 156,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 340,31</t>
+          <t>1,8; 381,11</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,28</t>
+          <t>0,75; 3,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,0</t>
+          <t>1,08; 3,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,99</t>
+          <t>1,41; 3,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 14,75</t>
+          <t>-0,21; 2,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,8; 209,14</t>
+          <t>27,34; 210,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,6; 145,06</t>
+          <t>22,98; 138,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,5; 167,84</t>
+          <t>42,22; 165,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 504,31</t>
+          <t>-4,47; 69,22</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,01</t>
+          <t>2,95</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>113,59%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 2,7</t>
+          <t>-2,61; 2,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 5,47</t>
+          <t>-1,39; 5,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,25</t>
+          <t>-0,27; 5,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,14</t>
+          <t>1,06; 5,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-51,24; 95,73</t>
+          <t>-50,22; 99,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 143,83</t>
+          <t>-22,71; 162,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 153,51</t>
+          <t>-7,13; 170,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,57; 295,99</t>
+          <t>23,33; 243,71</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,08</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>48,46%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,37</t>
+          <t>0,74; 2,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,06</t>
+          <t>1,09; 3,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,27</t>
+          <t>1,47; 3,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 10,34</t>
+          <t>0,67; 2,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,13; 120,77</t>
+          <t>25,93; 123,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,65; 100,69</t>
+          <t>27,27; 107,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,81; 124,99</t>
+          <t>39,92; 125,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,25; 385,69</t>
+          <t>17,98; 87,69</t>
         </is>
       </c>
     </row>
